--- a/mlb_bets.xlsx
+++ b/mlb_bets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\PycharmProjects\ajo\mlb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE614049-86BA-49C3-AAC8-DF2AE65ED114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A8DBF6-0C08-4E07-912D-DD9FC9C73765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F06E2587-9A74-4010-AEF7-C17604D46CA5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F06E2587-9A74-4010-AEF7-C17604D46CA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,42 +25,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Andrew Chang</author>
-  </authors>
-  <commentList>
-    <comment ref="D65" authorId="0" shapeId="0" xr:uid="{F9C7D3F8-65FA-4D79-A17C-2153E162447B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Andrew Chang:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Won $1000 on the 24/03/2026 at the star</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>bet</t>
   </si>
@@ -86,14 +52,50 @@
     <t>net</t>
   </si>
   <si>
-    <t>The star</t>
+    <t>rolling</t>
+  </si>
+  <si>
+    <t>0 Runs @ 1.80</t>
+  </si>
+  <si>
+    <t>Erick Fedde Over (3.5) @ 1.70</t>
+  </si>
+  <si>
+    <t>JR Ritchie Over (4.5) @ 1.69</t>
+  </si>
+  <si>
+    <t>Yusei Kikuchi Under (5.5) @ 2.04</t>
+  </si>
+  <si>
+    <t>Gavin Williams Over (5.5) @ 1.77</t>
+  </si>
+  <si>
+    <t>George Kirby Over (5.5) @ 2.25</t>
+  </si>
+  <si>
+    <t>Under (52.5) @ 1.96</t>
+  </si>
+  <si>
+    <t>Miles Mikolas Over (3.5) @ 2.11</t>
+  </si>
+  <si>
+    <t>Jeffrey Springs Over (4.5) @ 2.05</t>
+  </si>
+  <si>
+    <t>Ryne Nelson Over (4.5) @ 1.99</t>
+  </si>
+  <si>
+    <t>Shota Imanaga Over (4.5) @ 1.67</t>
+  </si>
+  <si>
+    <t>Roki Sasaki Over (4.5) @ 2.12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,32 +103,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -156,22 +139,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -296,10 +272,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$J$3:$J$38</c:f>
+              <c:f>Sheet1!$J$3:$J$241</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="239"/>
                 <c:pt idx="0">
                   <c:v>46107</c:v>
                 </c:pt>
@@ -407,16 +383,34 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46143</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46144</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46145</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$M$3:$M$38</c:f>
+              <c:f>Sheet1!$M$3:$M$241</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="239"/>
                 <c:pt idx="0">
                   <c:v>57.44</c:v>
                 </c:pt>
@@ -439,25 +433,25 @@
                   <c:v>-21</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-350</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>-148</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-130</c:v>
+                  <c:v>-127</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>-373</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-50</c:v>
+                  <c:v>86.12</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>-50</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>-50</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
@@ -466,7 +460,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>-50</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0</c:v>
@@ -478,7 +472,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>-10</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -487,13 +481,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>-175</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>-50</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0</c:v>
@@ -502,7 +496,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0</c:v>
+                  <c:v>-50</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0</c:v>
@@ -511,18 +505,36 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0</c:v>
+                  <c:v>-50</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0</c:v>
+                  <c:v>-50</c:v>
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0</c:v>
+                  <c:v>109.75999999999999</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>-50</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-400</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-133</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -632,10 +644,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$J$3:$J$38</c:f>
+              <c:f>Sheet1!$J$3:$J$241</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="239"/>
                 <c:pt idx="0">
                   <c:v>46107</c:v>
                 </c:pt>
@@ -743,16 +755,34 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46143</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46144</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46145</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$K$3:$K$38</c:f>
+              <c:f>Sheet1!$K$3:$K$241</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="239"/>
                 <c:pt idx="0">
                   <c:v>182</c:v>
                 </c:pt>
@@ -775,7 +805,7 @@
                   <c:v>911.53</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2331.5</c:v>
+                  <c:v>831.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>431.5</c:v>
@@ -787,13 +817,13 @@
                   <c:v>373</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>50</c:v>
+                  <c:v>203</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
@@ -802,7 +832,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0</c:v>
@@ -814,7 +844,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -823,13 +853,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>175</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0</c:v>
@@ -838,7 +868,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0</c:v>
@@ -847,18 +877,36 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0</c:v>
+                  <c:v>136.5</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>601</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -953,10 +1001,10 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$J$3:$J$38</c:f>
+              <c:f>Sheet1!$J$3:$J$241</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="239"/>
                 <c:pt idx="0">
                   <c:v>46107</c:v>
                 </c:pt>
@@ -1064,16 +1112,34 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46143</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46144</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46145</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$3:$L$38</c:f>
+              <c:f>Sheet1!$L$3:$L$241</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="239"/>
                 <c:pt idx="0">
                   <c:v>239.44</c:v>
                 </c:pt>
@@ -1096,19 +1162,19 @@
                   <c:v>890.53</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1981.5</c:v>
+                  <c:v>981.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>283.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>363</c:v>
+                  <c:v>366</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>289.12</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -1135,7 +1201,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -1177,9 +1243,27 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0</c:v>
+                  <c:v>246.26</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>551</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1381,7 +1465,591 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$N$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>rolling</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$J$3:$J$102</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="0">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46109</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46110</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46116</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46117</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46118</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46123</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46124</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46130</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46131</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46137</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46138</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46143</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46144</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46145</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46148</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$N$3:$N$102</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="100"/>
+                <c:pt idx="1">
+                  <c:v>179.94</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>351.53999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>653.83999999999992</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>835.82999999999993</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>690.82999999999993</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>669.82999999999993</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>819.82999999999993</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>671.82999999999993</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>544.82999999999993</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>171.82999999999993</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>257.94999999999993</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>207.94999999999993</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>157.94999999999993</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>157.94999999999993</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>157.94999999999993</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>107.94999999999993</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>107.94999999999993</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>107.94999999999993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>107.94999999999993</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>97.949999999999932</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>97.949999999999932</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>97.949999999999932</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-77.050000000000068</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-77.050000000000068</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-127.05000000000007</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-127.05000000000007</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-127.05000000000007</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-177.05000000000007</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-177.05000000000007</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-177.05000000000007</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-227.05000000000007</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-277.05000000000007</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-277.05000000000007</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-167.29000000000008</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-217.29000000000008</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-617.29000000000008</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-569.29000000000008</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-759.73</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-702.29000000000008</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-702.29000000000008</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-702.29000000000008</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-033A-4DD2-9371-8123798F889A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="880375072"/>
+        <c:axId val="880375552"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="880375072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="880375552"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="880375552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="880375072"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1937,20 +2605,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>390526</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>23813</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>447676</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>147638</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>47626</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>104776</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1970,6 +3154,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>200024</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>176211</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>495299</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E61C8E02-AAA3-DEB7-836A-9E080B1C3D4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2274,16 +3494,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5E4DA3F-5F53-4185-913C-D95CCA552531}">
-  <dimension ref="B2:M77"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5E4DA3F-5F53-4185-913C-D95CCA552531}">
+  <dimension ref="B2:N103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="3"/>
+    <col min="2" max="2" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="2"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2299,7 +3520,7 @@
       <c r="H2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -2311,9 +3532,12 @@
       <c r="M2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="4">
+      <c r="N2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B3" s="3">
         <v>46107</v>
       </c>
       <c r="C3" s="1">
@@ -2323,42 +3547,43 @@
         <v>82</v>
       </c>
       <c r="F3" s="1">
-        <f>SUM(C3:C9999)</f>
-        <v>7586.08</v>
+        <f>SUM(C3:C9998)</f>
+        <v>8245.58</v>
       </c>
       <c r="G3" s="1">
-        <f>SUM(D3:D9999)</f>
-        <v>7154.91</v>
+        <f>SUM(D3:D9998)</f>
+        <v>7543.29</v>
       </c>
       <c r="H3" s="1">
         <f>G3-F3</f>
-        <v>-431.17000000000007</v>
-      </c>
-      <c r="J3" s="4">
+        <v>-702.29</v>
+      </c>
+      <c r="J3" s="3">
         <v>46107</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" ref="K3:K10" si="0">SUMIF(B:B,J3,C:C)</f>
+        <f t="shared" ref="K3:K44" si="0">SUMIF(B:B,J3,C:C)</f>
         <v>182</v>
       </c>
       <c r="L3" s="1">
-        <f t="shared" ref="L3:L10" si="1">SUMIF(B:B,J3,D:D)</f>
+        <f t="shared" ref="L3:L44" si="1">SUMIF(B:B,J3,D:D)</f>
         <v>239.44</v>
       </c>
       <c r="M3" s="1">
         <f>L3-K3</f>
         <v>57.44</v>
       </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="4">
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B4" s="3">
         <v>46107</v>
       </c>
       <c r="C4" s="1">
         <v>50</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>46108</v>
       </c>
       <c r="K4" s="1">
@@ -2373,9 +3598,13 @@
         <f t="shared" ref="M4:M8" si="2">L4-K4</f>
         <v>122.5</v>
       </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="4">
+      <c r="N4" s="1">
+        <f>SUM(M3:M4)</f>
+        <v>179.94</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B5" s="3">
         <v>46107</v>
       </c>
       <c r="C5" s="1">
@@ -2384,7 +3613,7 @@
       <c r="D5" s="1">
         <v>157.44</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>46109</v>
       </c>
       <c r="K5" s="1">
@@ -2399,9 +3628,13 @@
         <f t="shared" si="2"/>
         <v>171.6</v>
       </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="4">
+      <c r="N5" s="1">
+        <f>SUM(M3:M5)</f>
+        <v>351.53999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
         <v>46108</v>
       </c>
       <c r="C6" s="1">
@@ -2410,7 +3643,7 @@
       <c r="D6" s="1">
         <v>144</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="3">
         <v>46110</v>
       </c>
       <c r="K6" s="1">
@@ -2425,9 +3658,13 @@
         <f t="shared" si="2"/>
         <v>302.29999999999995</v>
       </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="4">
+      <c r="N6" s="1">
+        <f>SUM(M3:M6)</f>
+        <v>653.83999999999992</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B7" s="3">
         <v>46108</v>
       </c>
       <c r="C7" s="1">
@@ -2436,7 +3673,7 @@
       <c r="D7" s="1">
         <v>35</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="3">
         <v>46111</v>
       </c>
       <c r="K7" s="1">
@@ -2451,16 +3688,20 @@
         <f t="shared" si="2"/>
         <v>181.99</v>
       </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="4">
+      <c r="N7" s="1">
+        <f>SUM(M3:M7)</f>
+        <v>835.82999999999993</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B8" s="3">
         <v>46108</v>
       </c>
       <c r="C8" s="1">
         <v>24</v>
       </c>
       <c r="D8" s="1"/>
-      <c r="J8" s="4">
+      <c r="J8" s="3">
         <v>46112</v>
       </c>
       <c r="K8" s="1">
@@ -2475,16 +3716,20 @@
         <f t="shared" si="2"/>
         <v>-145</v>
       </c>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="4">
+      <c r="N8" s="1">
+        <f>SUM(M3:M8)</f>
+        <v>690.82999999999993</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B9" s="3">
         <v>46108</v>
       </c>
       <c r="C9" s="1">
         <v>35</v>
       </c>
       <c r="D9" s="1"/>
-      <c r="J9" s="4">
+      <c r="J9" s="3">
         <v>46113</v>
       </c>
       <c r="K9" s="1">
@@ -2499,9 +3744,13 @@
         <f t="shared" ref="M9" si="3">L9-K9</f>
         <v>-21</v>
       </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="4">
+      <c r="N9" s="1">
+        <f>SUM(M3:M9)</f>
+        <v>669.82999999999993</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B10" s="3">
         <v>46108</v>
       </c>
       <c r="C10" s="1">
@@ -2510,49 +3759,57 @@
       <c r="D10" s="1">
         <v>172.5</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="3">
         <v>46114</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" si="0"/>
-        <v>2331.5</v>
+        <v>831.5</v>
       </c>
       <c r="L10" s="1">
         <f t="shared" si="1"/>
-        <v>1981.5</v>
+        <v>981.5</v>
       </c>
       <c r="M10" s="1">
         <f t="shared" ref="M10" si="4">L10-K10</f>
-        <v>-350</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="4">
+        <v>150</v>
+      </c>
+      <c r="N10" s="1">
+        <f>SUM(M3:M10)</f>
+        <v>819.82999999999993</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B11" s="3">
         <v>46108</v>
       </c>
       <c r="C11" s="1">
         <v>50</v>
       </c>
       <c r="D11" s="1"/>
-      <c r="J11" s="4">
+      <c r="J11" s="3">
         <f>J10+1</f>
         <v>46115</v>
       </c>
       <c r="K11" s="1">
-        <f t="shared" ref="K11:K39" si="5">SUMIF(B:B,J11,C:C)</f>
+        <f t="shared" si="0"/>
         <v>431.5</v>
       </c>
       <c r="L11" s="1">
-        <f t="shared" ref="L11:L39" si="6">SUMIF(B:B,J11,D:D)</f>
+        <f t="shared" si="1"/>
         <v>283.5</v>
       </c>
       <c r="M11" s="1">
-        <f t="shared" ref="M11:M39" si="7">L11-K11</f>
+        <f t="shared" ref="M11:M39" si="5">L11-K11</f>
         <v>-148</v>
       </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="4">
+      <c r="N11" s="1">
+        <f>SUM(M3:M11)</f>
+        <v>671.82999999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B12" s="3">
         <v>46109</v>
       </c>
       <c r="C12" s="1">
@@ -2561,25 +3818,29 @@
       <c r="D12" s="1">
         <v>95.45</v>
       </c>
-      <c r="J12" s="4">
-        <f t="shared" ref="J12:J39" si="8">J11+1</f>
+      <c r="J12" s="3">
+        <f t="shared" ref="J12:J44" si="6">J11+1</f>
         <v>46116</v>
       </c>
       <c r="K12" s="1">
+        <f t="shared" si="0"/>
+        <v>493</v>
+      </c>
+      <c r="L12" s="1">
+        <f t="shared" si="1"/>
+        <v>366</v>
+      </c>
+      <c r="M12" s="1">
         <f t="shared" si="5"/>
-        <v>493</v>
-      </c>
-      <c r="L12" s="1">
-        <f t="shared" si="6"/>
-        <v>363</v>
-      </c>
-      <c r="M12" s="1">
-        <f t="shared" si="7"/>
-        <v>-130</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="4">
+        <v>-127</v>
+      </c>
+      <c r="N12" s="1">
+        <f>SUM(M3:M12)</f>
+        <v>544.82999999999993</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B13" s="3">
         <v>46109</v>
       </c>
       <c r="C13" s="1">
@@ -2588,25 +3849,29 @@
       <c r="D13" s="1">
         <v>79.08</v>
       </c>
-      <c r="J13" s="4">
-        <f t="shared" si="8"/>
+      <c r="J13" s="3">
+        <f t="shared" si="6"/>
         <v>46117</v>
       </c>
       <c r="K13" s="1">
+        <f t="shared" si="0"/>
+        <v>373</v>
+      </c>
+      <c r="L13" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
         <f t="shared" si="5"/>
-        <v>373</v>
-      </c>
-      <c r="L13" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <f t="shared" si="7"/>
         <v>-373</v>
       </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="4">
+      <c r="N13" s="1">
+        <f>SUM(M3:M13)</f>
+        <v>171.82999999999993</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B14" s="3">
         <v>46109</v>
       </c>
       <c r="C14" s="1">
@@ -2615,25 +3880,29 @@
       <c r="D14" s="1">
         <v>50.6</v>
       </c>
-      <c r="J14" s="4">
-        <f t="shared" si="8"/>
+      <c r="J14" s="3">
+        <f t="shared" si="6"/>
         <v>46118</v>
       </c>
       <c r="K14" s="1">
+        <f t="shared" si="0"/>
+        <v>203</v>
+      </c>
+      <c r="L14" s="1">
+        <f t="shared" si="1"/>
+        <v>289.12</v>
+      </c>
+      <c r="M14" s="1">
         <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-      <c r="L14" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <f t="shared" si="7"/>
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B15" s="4">
+        <v>86.12</v>
+      </c>
+      <c r="N14" s="1">
+        <f>SUM(M3:M14)</f>
+        <v>257.94999999999993</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B15" s="3">
         <v>46109</v>
       </c>
       <c r="C15" s="1">
@@ -2642,25 +3911,29 @@
       <c r="D15" s="1">
         <v>96</v>
       </c>
-      <c r="J15" s="4">
-        <f t="shared" si="8"/>
+      <c r="J15" s="3">
+        <f t="shared" si="6"/>
         <v>46119</v>
       </c>
       <c r="K15" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="L15" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
         <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-      <c r="L15" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="1">
-        <f t="shared" si="7"/>
         <v>-50</v>
       </c>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B16" s="4">
+      <c r="N15" s="1">
+        <f>SUM(M3:M15)</f>
+        <v>207.94999999999993</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B16" s="3">
         <v>46110</v>
       </c>
       <c r="C16" s="1">
@@ -2669,75 +3942,87 @@
       <c r="D16" s="1">
         <v>198</v>
       </c>
-      <c r="J16" s="4">
-        <f t="shared" si="8"/>
+      <c r="J16" s="3">
+        <f t="shared" si="6"/>
         <v>46120</v>
       </c>
       <c r="K16" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="L16" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B17" s="4">
+        <v>-50</v>
+      </c>
+      <c r="N16" s="1">
+        <f>SUM(M3:M16)</f>
+        <v>157.94999999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B17" s="3">
         <v>46110</v>
       </c>
       <c r="C17" s="1">
         <v>25</v>
       </c>
       <c r="D17" s="1"/>
-      <c r="J17" s="4">
-        <f t="shared" si="8"/>
+      <c r="J17" s="3">
+        <f t="shared" si="6"/>
         <v>46121</v>
       </c>
       <c r="K17" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L17" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B18" s="4">
+      <c r="N17" s="1">
+        <f>SUM(M3:M17)</f>
+        <v>157.94999999999993</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B18" s="3">
         <v>46110</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
       </c>
       <c r="D18" s="1"/>
-      <c r="J18" s="4">
-        <f t="shared" si="8"/>
+      <c r="J18" s="3">
+        <f t="shared" si="6"/>
         <v>46122</v>
       </c>
       <c r="K18" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L18" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B19" s="4">
+      <c r="N18" s="1">
+        <f>SUM(M3:M18)</f>
+        <v>157.94999999999993</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B19" s="3">
         <v>46110</v>
       </c>
       <c r="C19" s="1">
@@ -2746,50 +4031,58 @@
       <c r="D19" s="1">
         <v>90.72</v>
       </c>
-      <c r="J19" s="4">
-        <f t="shared" si="8"/>
+      <c r="J19" s="3">
+        <f t="shared" si="6"/>
         <v>46123</v>
       </c>
       <c r="K19" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="L19" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B20" s="4">
+        <v>-50</v>
+      </c>
+      <c r="N19" s="1">
+        <f>SUM(M3:M19)</f>
+        <v>107.94999999999993</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B20" s="3">
         <v>46110</v>
       </c>
       <c r="C20" s="1">
         <v>50.72</v>
       </c>
       <c r="D20" s="1"/>
-      <c r="J20" s="4">
-        <f t="shared" si="8"/>
+      <c r="J20" s="3">
+        <f t="shared" si="6"/>
         <v>46124</v>
       </c>
       <c r="K20" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L20" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B21" s="4">
+      <c r="N20" s="1">
+        <f>SUM(M3:M20)</f>
+        <v>107.94999999999993</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B21" s="3">
         <v>46110</v>
       </c>
       <c r="C21" s="1">
@@ -2798,25 +4091,29 @@
       <c r="D21" s="1">
         <v>189</v>
       </c>
-      <c r="J21" s="4">
-        <f t="shared" si="8"/>
+      <c r="J21" s="3">
+        <f t="shared" si="6"/>
         <v>46125</v>
       </c>
       <c r="K21" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L21" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B22" s="4">
+      <c r="N21" s="1">
+        <f>SUM(M3:M21)</f>
+        <v>107.94999999999993</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B22" s="3">
         <v>46110</v>
       </c>
       <c r="C22" s="1">
@@ -2825,25 +4122,29 @@
       <c r="D22" s="1">
         <v>69.2</v>
       </c>
-      <c r="J22" s="4">
-        <f t="shared" si="8"/>
+      <c r="J22" s="3">
+        <f t="shared" si="6"/>
         <v>46126</v>
       </c>
       <c r="K22" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L22" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B23" s="4">
+      <c r="N22" s="1">
+        <f>SUM(M3:M22)</f>
+        <v>107.94999999999993</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B23" s="3">
         <v>46110</v>
       </c>
       <c r="C23" s="1">
@@ -2852,25 +4153,29 @@
       <c r="D23" s="1">
         <v>79.3</v>
       </c>
-      <c r="J23" s="4">
-        <f t="shared" si="8"/>
+      <c r="J23" s="3">
+        <f t="shared" si="6"/>
         <v>46127</v>
       </c>
       <c r="K23" s="1">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="L23" s="1">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="M23" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B24" s="4">
+        <v>-10</v>
+      </c>
+      <c r="N23" s="1">
+        <f>SUM(M3:M23)</f>
+        <v>97.949999999999932</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B24" s="3">
         <v>46110</v>
       </c>
       <c r="C24" s="1">
@@ -2879,25 +4184,29 @@
       <c r="D24" s="1">
         <v>178</v>
       </c>
-      <c r="J24" s="4">
-        <f t="shared" si="8"/>
+      <c r="J24" s="3">
+        <f t="shared" si="6"/>
         <v>46128</v>
       </c>
       <c r="K24" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L24" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B25" s="4">
+      <c r="N24" s="1">
+        <f>SUM(M3:M24)</f>
+        <v>97.949999999999932</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B25" s="3">
         <v>46110</v>
       </c>
       <c r="C25" s="1">
@@ -2906,75 +4215,87 @@
       <c r="D25" s="1">
         <v>72</v>
       </c>
-      <c r="J25" s="4">
-        <f t="shared" si="8"/>
+      <c r="J25" s="3">
+        <f t="shared" si="6"/>
         <v>46129</v>
       </c>
       <c r="K25" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L25" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B26" s="4">
+      <c r="N25" s="1">
+        <f>SUM(M3:M25)</f>
+        <v>97.949999999999932</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B26" s="3">
         <v>46111</v>
       </c>
       <c r="C26" s="1">
         <v>50</v>
       </c>
       <c r="D26" s="1"/>
-      <c r="J26" s="4">
-        <f t="shared" si="8"/>
+      <c r="J26" s="3">
+        <f t="shared" si="6"/>
         <v>46130</v>
       </c>
       <c r="K26" s="1">
+        <f t="shared" si="0"/>
+        <v>175</v>
+      </c>
+      <c r="L26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B27" s="4">
+        <v>-175</v>
+      </c>
+      <c r="N26" s="1">
+        <f>SUM(M3:M26)</f>
+        <v>-77.050000000000068</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B27" s="3">
         <v>46111</v>
       </c>
       <c r="C27" s="1">
         <v>50</v>
       </c>
       <c r="D27" s="1"/>
-      <c r="J27" s="4">
-        <f t="shared" si="8"/>
+      <c r="J27" s="3">
+        <f t="shared" si="6"/>
         <v>46131</v>
       </c>
       <c r="K27" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L27" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M27" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B28" s="4">
+      <c r="N27" s="1">
+        <f>SUM(M3:M27)</f>
+        <v>-77.050000000000068</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B28" s="3">
         <v>46111</v>
       </c>
       <c r="C28" s="1">
@@ -2983,25 +4304,29 @@
       <c r="D28" s="1">
         <v>102.5</v>
       </c>
-      <c r="J28" s="4">
-        <f t="shared" si="8"/>
+      <c r="J28" s="3">
+        <f t="shared" si="6"/>
         <v>46132</v>
       </c>
       <c r="K28" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="L28" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M28" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B29" s="4">
+        <v>-50</v>
+      </c>
+      <c r="N28" s="1">
+        <f>SUM(M3:M28)</f>
+        <v>-127.05000000000007</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B29" s="3">
         <v>46111</v>
       </c>
       <c r="C29" s="1">
@@ -3010,25 +4335,29 @@
       <c r="D29" s="1">
         <v>85.5</v>
       </c>
-      <c r="J29" s="4">
-        <f t="shared" si="8"/>
+      <c r="J29" s="3">
+        <f t="shared" si="6"/>
         <v>46133</v>
       </c>
       <c r="K29" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L29" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B30" s="4">
+      <c r="N29" s="1">
+        <f>SUM(M3:M29)</f>
+        <v>-127.05000000000007</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B30" s="3">
         <v>46111</v>
       </c>
       <c r="C30" s="1">
@@ -3037,25 +4366,29 @@
       <c r="D30" s="1">
         <v>97</v>
       </c>
-      <c r="J30" s="4">
+      <c r="J30" s="3">
         <f>J29+1</f>
         <v>46134</v>
       </c>
       <c r="K30" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L30" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M30" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B31" s="4">
+      <c r="N30" s="1">
+        <f>SUM(M3:M30)</f>
+        <v>-127.05000000000007</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B31" s="3">
         <v>46111</v>
       </c>
       <c r="C31" s="1">
@@ -3064,75 +4397,87 @@
       <c r="D31" s="1">
         <v>87</v>
       </c>
-      <c r="J31" s="4">
-        <f t="shared" si="8"/>
+      <c r="J31" s="3">
+        <f t="shared" si="6"/>
         <v>46135</v>
       </c>
       <c r="K31" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="L31" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L31" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M31" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B32" s="4">
+        <v>-50</v>
+      </c>
+      <c r="N31" s="1">
+        <f>SUM(M3:M31)</f>
+        <v>-177.05000000000007</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B32" s="3">
         <v>46111</v>
       </c>
       <c r="C32" s="1">
         <v>50</v>
       </c>
       <c r="D32" s="1"/>
-      <c r="J32" s="4">
-        <f t="shared" si="8"/>
+      <c r="J32" s="3">
+        <f t="shared" si="6"/>
         <v>46136</v>
       </c>
       <c r="K32" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L32" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M32" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B33" s="4">
+      <c r="N32" s="1">
+        <f>SUM(M3:M32)</f>
+        <v>-177.05000000000007</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B33" s="3">
         <v>46111</v>
       </c>
       <c r="C33" s="1">
         <v>50</v>
       </c>
       <c r="D33" s="1"/>
-      <c r="J33" s="4">
-        <f t="shared" si="8"/>
+      <c r="J33" s="3">
+        <f t="shared" si="6"/>
         <v>46137</v>
       </c>
       <c r="K33" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L33" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M33" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B34" s="4">
+      <c r="N33" s="1">
+        <f>SUM(M3:M33)</f>
+        <v>-177.05000000000007</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B34" s="3">
         <v>46111</v>
       </c>
       <c r="C34" s="1">
@@ -3141,25 +4486,29 @@
       <c r="D34" s="1">
         <v>310.64</v>
       </c>
-      <c r="J34" s="4">
-        <f t="shared" si="8"/>
+      <c r="J34" s="3">
+        <f t="shared" si="6"/>
         <v>46138</v>
       </c>
       <c r="K34" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="L34" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L34" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M34" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B35" s="4">
+        <v>-50</v>
+      </c>
+      <c r="N34" s="1">
+        <f>SUM(M3:M34)</f>
+        <v>-227.05000000000007</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B35" s="3">
         <v>46111</v>
       </c>
       <c r="C35" s="1">
@@ -3168,25 +4517,29 @@
       <c r="D35" s="1">
         <v>67.45</v>
       </c>
-      <c r="J35" s="4">
-        <f t="shared" si="8"/>
+      <c r="J35" s="3">
+        <f t="shared" si="6"/>
         <v>46139</v>
       </c>
       <c r="K35" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="L35" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L35" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M35" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B36" s="4">
+        <v>-50</v>
+      </c>
+      <c r="N35" s="1">
+        <f>SUM(M3:M35)</f>
+        <v>-277.05000000000007</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B36" s="3">
         <v>46111</v>
       </c>
       <c r="C36" s="1">
@@ -3195,25 +4548,29 @@
       <c r="D36" s="1">
         <v>94</v>
       </c>
-      <c r="J36" s="4">
-        <f t="shared" si="8"/>
+      <c r="J36" s="3">
+        <f t="shared" si="6"/>
         <v>46140</v>
       </c>
       <c r="K36" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L36" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M36" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B37" s="4">
+      <c r="N36" s="1">
+        <f>SUM(M3:M36)</f>
+        <v>-277.05000000000007</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B37" s="3">
         <v>46112</v>
       </c>
       <c r="C37" s="1">
@@ -3222,84 +4579,116 @@
       <c r="D37" s="1">
         <v>199</v>
       </c>
-      <c r="J37" s="4">
-        <f t="shared" si="8"/>
+      <c r="J37" s="3">
+        <f t="shared" si="6"/>
         <v>46141</v>
       </c>
       <c r="K37" s="1">
+        <f t="shared" si="0"/>
+        <v>136.5</v>
+      </c>
+      <c r="L37" s="1">
+        <f t="shared" si="1"/>
+        <v>246.26</v>
+      </c>
+      <c r="M37" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L37" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M37" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B38" s="4">
+        <v>109.75999999999999</v>
+      </c>
+      <c r="N37" s="1">
+        <f>SUM(M3:M37)</f>
+        <v>-167.29000000000008</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B38" s="3">
         <v>46112</v>
       </c>
       <c r="C38" s="1">
         <v>50</v>
       </c>
       <c r="D38" s="1"/>
-      <c r="J38" s="4">
-        <f t="shared" si="8"/>
+      <c r="J38" s="3">
+        <f t="shared" si="6"/>
         <v>46142</v>
       </c>
       <c r="K38" s="1">
+        <f t="shared" si="0"/>
+        <v>601</v>
+      </c>
+      <c r="L38" s="1">
+        <f t="shared" si="1"/>
+        <v>551</v>
+      </c>
+      <c r="M38" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L38" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M38" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B39" s="4">
+        <v>-50</v>
+      </c>
+      <c r="N38" s="1">
+        <f>SUM(M3:M38)</f>
+        <v>-217.29000000000008</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B39" s="3">
         <v>46112</v>
       </c>
       <c r="C39" s="1">
         <v>100</v>
       </c>
       <c r="D39" s="1"/>
-      <c r="J39" s="4">
-        <f t="shared" si="8"/>
+      <c r="J39" s="3">
+        <f t="shared" si="6"/>
         <v>46143</v>
       </c>
       <c r="K39" s="1">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="L39" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L39" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M39" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B40" s="4">
+        <v>-400</v>
+      </c>
+      <c r="N39" s="1">
+        <f>SUM(M3:M39)</f>
+        <v>-617.29000000000008</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B40" s="3">
         <v>46112</v>
       </c>
       <c r="C40" s="1">
         <v>100</v>
       </c>
       <c r="D40" s="1"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B41" s="4">
+      <c r="J40" s="3">
+        <f t="shared" si="6"/>
+        <v>46144</v>
+      </c>
+      <c r="K40" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="L40" s="1">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="M40" s="1">
+        <f t="shared" ref="M40:M44" si="7">L40-K40</f>
+        <v>48</v>
+      </c>
+      <c r="N40" s="1">
+        <f>SUM(M3:M40)</f>
+        <v>-569.29000000000008</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B41" s="3">
         <v>46112</v>
       </c>
       <c r="C41" s="1">
@@ -3308,18 +4697,58 @@
       <c r="D41" s="1">
         <v>182</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B42" s="4">
+      <c r="J41" s="3">
+        <f t="shared" si="6"/>
+        <v>46145</v>
+      </c>
+      <c r="K41" s="1">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="L41" s="1">
+        <f t="shared" si="1"/>
+        <v>167</v>
+      </c>
+      <c r="M41" s="1">
+        <f t="shared" si="7"/>
+        <v>-133</v>
+      </c>
+      <c r="N41" s="1">
+        <f>SUM(M4:M41)</f>
+        <v>-759.73</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B42" s="3">
         <v>46112</v>
       </c>
       <c r="C42" s="1">
         <v>99</v>
       </c>
       <c r="D42" s="1"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B43" s="4">
+      <c r="J42" s="3">
+        <f t="shared" si="6"/>
+        <v>46146</v>
+      </c>
+      <c r="K42" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N42" s="1">
+        <f>SUM(M3:M42)</f>
+        <v>-702.29000000000008</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B43" s="3">
         <v>46112</v>
       </c>
       <c r="C43" s="1">
@@ -3328,18 +4757,58 @@
       <c r="D43" s="1">
         <v>191</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B44" s="4">
+      <c r="J43" s="3">
+        <f t="shared" si="6"/>
+        <v>46147</v>
+      </c>
+      <c r="K43" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N43" s="1">
+        <f>SUM(M3:M43)</f>
+        <v>-702.29000000000008</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B44" s="3">
         <v>46112</v>
       </c>
       <c r="C44" s="1">
         <v>100</v>
       </c>
       <c r="D44" s="1"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B45" s="4">
+      <c r="J44" s="3">
+        <f t="shared" si="6"/>
+        <v>46148</v>
+      </c>
+      <c r="K44" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
+        <f>SUM(M3:M44)</f>
+        <v>-702.29000000000008</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B45" s="3">
         <v>46112</v>
       </c>
       <c r="C45" s="1">
@@ -3347,8 +4816,8 @@
       </c>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B46" s="4">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B46" s="3">
         <v>46112</v>
       </c>
       <c r="C46" s="1">
@@ -3356,8 +4825,8 @@
       </c>
       <c r="D46" s="1"/>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B47" s="4">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B47" s="3">
         <v>46112</v>
       </c>
       <c r="C47" s="1">
@@ -3367,8 +4836,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B48" s="4">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B48" s="3">
         <v>46112</v>
       </c>
       <c r="C48" s="1">
@@ -3379,7 +4848,7 @@
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B49" s="4">
+      <c r="B49" s="3">
         <v>46113</v>
       </c>
       <c r="C49" s="1">
@@ -3390,7 +4859,7 @@
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B50" s="4">
+      <c r="B50" s="3">
         <v>46113</v>
       </c>
       <c r="C50" s="1">
@@ -3401,7 +4870,7 @@
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B51" s="4">
+      <c r="B51" s="3">
         <v>46113</v>
       </c>
       <c r="C51" s="1">
@@ -3410,7 +4879,7 @@
       <c r="D51" s="1"/>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B52" s="4">
+      <c r="B52" s="3">
         <v>46113</v>
       </c>
       <c r="C52" s="1">
@@ -3419,7 +4888,7 @@
       <c r="D52" s="1"/>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B53" s="4">
+      <c r="B53" s="3">
         <v>46113</v>
       </c>
       <c r="C53" s="1">
@@ -3430,7 +4899,7 @@
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B54" s="4">
+      <c r="B54" s="3">
         <v>46113</v>
       </c>
       <c r="C54" s="1">
@@ -3439,7 +4908,7 @@
       <c r="D54" s="1"/>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="4">
+      <c r="B55" s="3">
         <v>46113</v>
       </c>
       <c r="C55" s="1">
@@ -3448,7 +4917,7 @@
       <c r="D55" s="1"/>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B56" s="4">
+      <c r="B56" s="3">
         <v>46113</v>
       </c>
       <c r="C56" s="1">
@@ -3459,7 +4928,7 @@
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B57" s="4">
+      <c r="B57" s="3">
         <v>46114</v>
       </c>
       <c r="C57" s="1">
@@ -3470,7 +4939,7 @@
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B58" s="4">
+      <c r="B58" s="3">
         <v>46114</v>
       </c>
       <c r="C58" s="1">
@@ -3481,7 +4950,7 @@
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B59" s="4">
+      <c r="B59" s="3">
         <v>46114</v>
       </c>
       <c r="C59" s="1">
@@ -3490,7 +4959,7 @@
       <c r="D59" s="1"/>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B60" s="4">
+      <c r="B60" s="3">
         <v>46114</v>
       </c>
       <c r="C60" s="1">
@@ -3499,7 +4968,7 @@
       <c r="D60" s="1"/>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B61" s="4">
+      <c r="B61" s="3">
         <v>46114</v>
       </c>
       <c r="C61" s="1">
@@ -3508,7 +4977,7 @@
       <c r="D61" s="1"/>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B62" s="4">
+      <c r="B62" s="3">
         <v>46114</v>
       </c>
       <c r="C62" s="1">
@@ -3519,7 +4988,7 @@
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B63" s="4">
+      <c r="B63" s="3">
         <v>46114</v>
       </c>
       <c r="C63" s="1">
@@ -3530,7 +4999,7 @@
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B64" s="4">
+      <c r="B64" s="3">
         <v>46114</v>
       </c>
       <c r="C64" s="1">
@@ -3538,51 +5007,46 @@
       </c>
       <c r="D64" s="1"/>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B65" s="5">
-        <v>46114</v>
-      </c>
-      <c r="C65" s="6">
-        <v>1500</v>
-      </c>
-      <c r="D65" s="6">
-        <v>1000</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B66" s="4">
+    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B65" s="3">
+        <v>46115</v>
+      </c>
+      <c r="C65" s="1">
+        <v>150</v>
+      </c>
+      <c r="D65" s="1">
+        <v>283.5</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B66" s="3">
         <v>46115</v>
       </c>
       <c r="C66" s="1">
         <v>150</v>
       </c>
-      <c r="D66" s="1">
-        <v>283.5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B67" s="4">
+      <c r="D66" s="1"/>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B67" s="3">
         <v>46115</v>
       </c>
       <c r="C67" s="1">
-        <v>150</v>
+        <v>131.5</v>
       </c>
       <c r="D67" s="1"/>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B68" s="4">
-        <v>46115</v>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B68" s="3">
+        <v>46116</v>
       </c>
       <c r="C68" s="1">
-        <v>131.5</v>
+        <v>100</v>
       </c>
       <c r="D68" s="1"/>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B69" s="4">
+    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B69" s="3">
         <v>46116</v>
       </c>
       <c r="C69" s="1">
@@ -3590,84 +5054,383 @@
       </c>
       <c r="D69" s="1"/>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B70" s="4">
+    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B70" s="3">
         <v>46116</v>
       </c>
       <c r="C70" s="1">
         <v>100</v>
       </c>
-      <c r="D70" s="1"/>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B71" s="4">
+      <c r="D70" s="1">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B71" s="3">
         <v>46116</v>
       </c>
       <c r="C71" s="1">
         <v>100</v>
       </c>
       <c r="D71" s="1">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B72" s="4">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B72" s="3">
         <v>46116</v>
       </c>
       <c r="C72" s="1">
+        <v>93</v>
+      </c>
+      <c r="D72" s="1"/>
+    </row>
+    <row r="73" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B73" s="3">
+        <v>46117</v>
+      </c>
+      <c r="C73" s="1">
+        <v>273</v>
+      </c>
+      <c r="D73" s="1"/>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B74" s="3">
+        <v>46117</v>
+      </c>
+      <c r="C74" s="1">
         <v>100</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D74" s="1"/>
+    </row>
+    <row r="75" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B75" s="3">
+        <v>46118</v>
+      </c>
+      <c r="C75" s="1">
+        <v>50</v>
+      </c>
+      <c r="D75" s="1"/>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B76" s="3">
+        <v>46118</v>
+      </c>
+      <c r="C76" s="1">
+        <v>50</v>
+      </c>
+      <c r="D76" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B77" s="3">
+        <v>46118</v>
+      </c>
+      <c r="C77" s="1">
+        <v>103</v>
+      </c>
+      <c r="D77" s="1">
+        <v>185.12</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B78" s="3">
+        <v>46119</v>
+      </c>
+      <c r="C78" s="1">
+        <v>50</v>
+      </c>
+      <c r="D78" s="1"/>
+    </row>
+    <row r="79" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B79" s="3">
+        <v>46120</v>
+      </c>
+      <c r="C79" s="1">
+        <v>50</v>
+      </c>
+      <c r="D79" s="1"/>
+    </row>
+    <row r="80" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B80" s="3">
+        <v>46123</v>
+      </c>
+      <c r="C80" s="1">
+        <v>50</v>
+      </c>
+      <c r="D80" s="1"/>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B81" s="3">
+        <v>46127</v>
+      </c>
+      <c r="C81" s="1">
+        <v>10</v>
+      </c>
+      <c r="D81" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B82" s="3">
+        <v>46127</v>
+      </c>
+      <c r="C82" s="1">
+        <v>34</v>
+      </c>
+      <c r="D82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B83" s="3">
+        <v>46130</v>
+      </c>
+      <c r="C83" s="1">
+        <v>75</v>
+      </c>
+      <c r="D83" s="1"/>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B84" s="3">
+        <v>46130</v>
+      </c>
+      <c r="C84" s="1">
+        <v>100</v>
+      </c>
+      <c r="D84" s="1"/>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B85" s="3">
+        <v>46132</v>
+      </c>
+      <c r="C85" s="1">
+        <v>50</v>
+      </c>
+      <c r="D85" s="1"/>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B86" s="3">
+        <v>46135</v>
+      </c>
+      <c r="C86" s="1">
+        <v>50</v>
+      </c>
+      <c r="D86" s="1"/>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B87" s="3">
+        <v>46138</v>
+      </c>
+      <c r="C87" s="1">
+        <v>50</v>
+      </c>
+      <c r="D87" s="1"/>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B88" s="3">
+        <v>46139</v>
+      </c>
+      <c r="C88" s="1">
+        <v>50</v>
+      </c>
+      <c r="D88" s="1"/>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B89" s="3">
+        <v>46141</v>
+      </c>
+      <c r="C89" s="1">
+        <v>50</v>
+      </c>
+      <c r="D89" s="1">
+        <v>86.5</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B90" s="3">
+        <v>46141</v>
+      </c>
+      <c r="C90" s="1">
+        <v>50</v>
+      </c>
+      <c r="D90" s="1">
+        <v>91.5</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B91" s="3">
+        <v>46141</v>
+      </c>
+      <c r="C91" s="1">
+        <v>36.5</v>
+      </c>
+      <c r="D91" s="1">
+        <v>68.260000000000005</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B92" s="3">
+        <v>46142</v>
+      </c>
+      <c r="C92" s="1">
+        <v>101</v>
+      </c>
+      <c r="D92" s="1"/>
+      <c r="E92" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B93" s="3">
+        <v>46142</v>
+      </c>
+      <c r="C93" s="1">
+        <v>100</v>
+      </c>
+      <c r="D93" s="1">
         <v>170</v>
       </c>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B73" s="4">
-        <v>46116</v>
-      </c>
-      <c r="C73" s="1">
-        <v>93</v>
-      </c>
-      <c r="D73" s="1"/>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B74" s="4">
-        <v>46117</v>
-      </c>
-      <c r="C74" s="1">
-        <v>273</v>
-      </c>
-      <c r="D74" s="1"/>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B75" s="4">
-        <v>46117</v>
-      </c>
-      <c r="C75" s="1">
+      <c r="E93" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B94" s="3">
+        <v>46142</v>
+      </c>
+      <c r="C94" s="1">
         <v>100</v>
       </c>
-      <c r="D75" s="1"/>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B76" s="7">
-        <v>46118</v>
-      </c>
-      <c r="C76" s="3">
+      <c r="D94" s="1"/>
+      <c r="E94" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B95" s="3">
+        <v>46142</v>
+      </c>
+      <c r="C95" s="1">
+        <v>100</v>
+      </c>
+      <c r="D95" s="1">
+        <v>204</v>
+      </c>
+      <c r="E95" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B96" s="3">
+        <v>46142</v>
+      </c>
+      <c r="C96" s="1">
+        <v>100</v>
+      </c>
+      <c r="D96" s="1">
+        <v>177</v>
+      </c>
+      <c r="E96" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B97" s="3">
+        <v>46142</v>
+      </c>
+      <c r="C97" s="1">
+        <v>100</v>
+      </c>
+      <c r="D97" s="1"/>
+      <c r="E97" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B98" s="3">
+        <v>46143</v>
+      </c>
+      <c r="C98" s="1">
+        <v>200</v>
+      </c>
+      <c r="D98" s="1"/>
+      <c r="E98" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B99" s="3">
+        <v>46143</v>
+      </c>
+      <c r="C99" s="1">
+        <v>200</v>
+      </c>
+      <c r="D99" s="1"/>
+      <c r="E99" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B100" s="3">
+        <v>46144</v>
+      </c>
+      <c r="C100" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B77" s="7">
-        <v>46119</v>
-      </c>
-      <c r="C77" s="3">
-        <v>50</v>
+      <c r="D100" s="1">
+        <v>98</v>
+      </c>
+      <c r="E100" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B101" s="4">
+        <v>46145</v>
+      </c>
+      <c r="C101" s="2">
+        <v>100</v>
+      </c>
+      <c r="D101" s="2">
+        <v>0</v>
+      </c>
+      <c r="E101" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B102" s="4">
+        <v>46145</v>
+      </c>
+      <c r="C102" s="2">
+        <v>100</v>
+      </c>
+      <c r="D102" s="2">
+        <v>167</v>
+      </c>
+      <c r="E102" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B103" s="4">
+        <v>46145</v>
+      </c>
+      <c r="C103" s="2">
+        <v>100</v>
+      </c>
+      <c r="D103" s="2">
+        <v>0</v>
+      </c>
+      <c r="E103" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
